--- a/香港現在上映電影 2025-09-01.xlsx
+++ b/香港現在上映電影 2025-09-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="116">
   <si>
     <t>英文名稱</t>
   </si>
@@ -52,12 +52,15 @@
     <t>凶器</t>
   </si>
   <si>
-    <t>危險人物</t>
+    <t>夢遊納米比亞沙漠</t>
   </si>
   <si>
     <t>長相黐守</t>
   </si>
   <si>
+    <t>神探零零甩</t>
+  </si>
+  <si>
     <t>壞蛋聯盟2</t>
   </si>
   <si>
@@ -67,27 +70,21 @@
     <t>超人</t>
   </si>
   <si>
-    <t>外星奇遇記</t>
-  </si>
-  <si>
     <t>F1電影</t>
   </si>
   <si>
+    <t>職業特工隊：最終清算</t>
+  </si>
+  <si>
     <t>錢財心愛物</t>
   </si>
   <si>
     <t>殺神Nobody 2</t>
   </si>
   <si>
-    <t>這個殺手不太冷</t>
-  </si>
-  <si>
     <t>衰鬼媽咪2</t>
   </si>
   <si>
-    <t>孤星淚</t>
-  </si>
-  <si>
     <t>侏羅紀世界：重生</t>
   </si>
   <si>
@@ -103,12 +100,15 @@
     <t>Weapons</t>
   </si>
   <si>
-    <t>Pulp Fiction</t>
+    <t>Desert of Namibia</t>
   </si>
   <si>
     <t>Together</t>
   </si>
   <si>
+    <t>The Naked Gun</t>
+  </si>
+  <si>
     <t>The Bad Guys 2</t>
   </si>
   <si>
@@ -118,27 +118,21 @@
     <t>Superman</t>
   </si>
   <si>
-    <t>Elio</t>
-  </si>
-  <si>
     <t>F1 The Movie</t>
   </si>
   <si>
+    <t>Mission: Impossible - The Final Reckoning</t>
+  </si>
+  <si>
     <t>Materialists</t>
   </si>
   <si>
     <t>Nobody 2</t>
   </si>
   <si>
-    <t>Léon: The Professional</t>
-  </si>
-  <si>
     <t>Freakier Friday</t>
   </si>
   <si>
-    <t>Les Misérables</t>
-  </si>
-  <si>
     <t>Jurassic World Rebirth</t>
   </si>
   <si>
@@ -154,7 +148,7 @@
     <t>6/8/2025</t>
   </si>
   <si>
-    <t>10/9/1994</t>
+    <t>1/7/2025</t>
   </si>
   <si>
     <t>7/8/2025</t>
@@ -172,21 +166,15 @@
     <t>25/6/2025</t>
   </si>
   <si>
+    <t>23/5/2025</t>
+  </si>
+  <si>
     <t>21/8/2025</t>
   </si>
   <si>
     <t>13/8/2025</t>
   </si>
   <si>
-    <t>14/9/1994</t>
-  </si>
-  <si>
-    <t>2/1/2012</t>
-  </si>
-  <si>
-    <t>1/7/2025</t>
-  </si>
-  <si>
     <t>28/8/2025</t>
   </si>
   <si>
@@ -199,39 +187,36 @@
     <t>恐怖、驚悚</t>
   </si>
   <si>
-    <t>犯罪、劇情</t>
+    <t>劇情</t>
   </si>
   <si>
     <t>恐怖、科幻</t>
   </si>
   <si>
+    <t>喜劇、動作、犯罪</t>
+  </si>
+  <si>
     <t>親子、喜劇、冒險、動畫</t>
   </si>
   <si>
     <t>動作、冒險、科幻、奇幻</t>
   </si>
   <si>
-    <t>親子、喜劇、冒險、科幻、動畫</t>
-  </si>
-  <si>
     <t>動作、劇情、體育</t>
   </si>
   <si>
+    <t>動作、冒險、驚悚</t>
+  </si>
+  <si>
     <t>浪漫、喜劇、劇情</t>
   </si>
   <si>
     <t>動作、喜劇、劇情、驚悚</t>
   </si>
   <si>
-    <t>驚悚、動作、犯罪、劇情</t>
-  </si>
-  <si>
     <t>親子、喜劇、奇幻</t>
   </si>
   <si>
-    <t>音樂劇、歷史、劇情</t>
-  </si>
-  <si>
     <t>動作、冒險、科幻</t>
   </si>
   <si>
@@ -241,7 +226,7 @@
     <t>2h 8m</t>
   </si>
   <si>
-    <t>2h 34m</t>
+    <t>2h 17m</t>
   </si>
   <si>
     <t>1h 42m</t>
@@ -256,27 +241,21 @@
     <t>2h 9m</t>
   </si>
   <si>
-    <t>1h 38m</t>
-  </si>
-  <si>
     <t>2h 35m</t>
   </si>
   <si>
+    <t>2h 49m</t>
+  </si>
+  <si>
     <t>1h 56m</t>
   </si>
   <si>
     <t>1h 29m</t>
   </si>
   <si>
-    <t>1h 55m</t>
-  </si>
-  <si>
     <t>1h 51m</t>
   </si>
   <si>
-    <t>2h 38m</t>
-  </si>
-  <si>
     <t>2h 14m</t>
   </si>
   <si>
@@ -289,61 +268,55 @@
     <t>III</t>
   </si>
   <si>
+    <t>IIB</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
-    <t>IIB</t>
-  </si>
-  <si>
-    <t>2.815億</t>
-  </si>
-  <si>
-    <t>17.48億</t>
-  </si>
-  <si>
-    <t>16.68億</t>
-  </si>
-  <si>
-    <t>2.183億</t>
-  </si>
-  <si>
-    <t>12.55億</t>
-  </si>
-  <si>
-    <t>39.38億</t>
-  </si>
-  <si>
-    <t>47.41億</t>
-  </si>
-  <si>
-    <t>11.87億</t>
-  </si>
-  <si>
-    <t>47.51億</t>
-  </si>
-  <si>
-    <t>6.635億</t>
-  </si>
-  <si>
-    <t>2.573億</t>
-  </si>
-  <si>
-    <t>3.532億</t>
-  </si>
-  <si>
-    <t>10.21億</t>
-  </si>
-  <si>
-    <t>34.53億</t>
-  </si>
-  <si>
-    <t>66.12億</t>
+    <t>2.814億</t>
+  </si>
+  <si>
+    <t>18.29億</t>
+  </si>
+  <si>
+    <t>2.190億</t>
+  </si>
+  <si>
+    <t>7.483億</t>
+  </si>
+  <si>
+    <t>13.87億</t>
+  </si>
+  <si>
+    <t>39.46億</t>
+  </si>
+  <si>
+    <t>47.66億</t>
+  </si>
+  <si>
+    <t>47.80億</t>
+  </si>
+  <si>
+    <t>46.61億</t>
+  </si>
+  <si>
+    <t>7.218億</t>
+  </si>
+  <si>
+    <t>2.775億</t>
+  </si>
+  <si>
+    <t>10.34億</t>
+  </si>
+  <si>
+    <t>66.69億</t>
   </si>
   <si>
     <t>1325萬</t>
   </si>
   <si>
-    <t>8.592億</t>
+    <t>8.964億</t>
   </si>
   <si>
     <t>97</t>
@@ -376,15 +349,9 @@
     <t>78</t>
   </si>
   <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>74</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>51</t>
   </si>
   <si>
@@ -392,6 +359,9 @@
   </si>
   <si>
     <t>21</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -787,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.7109375" style="1" customWidth="1"/>
@@ -840,19 +810,19 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G2" s="1">
         <v>200</v>
@@ -864,10 +834,10 @@
         <v>500</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -875,19 +845,19 @@
         <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="G3" s="1">
         <v>343</v>
@@ -899,45 +869,42 @@
         <v>10000</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>29</v>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="G4" s="1">
-        <v>186</v>
-      </c>
-      <c r="H4" s="1">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -945,19 +912,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G5" s="1">
         <v>219</v>
@@ -969,10 +936,10 @@
         <v>1000</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -980,34 +947,31 @@
         <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G6" s="1">
-        <v>97</v>
+        <v>307</v>
       </c>
       <c r="H6" s="1">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="I6" s="1">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1015,34 +979,34 @@
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G7" s="1">
-        <v>388</v>
+        <v>97</v>
       </c>
       <c r="H7" s="1">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I7" s="1">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1050,34 +1014,34 @@
         <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="G8" s="1">
-        <v>483</v>
+        <v>388</v>
       </c>
       <c r="H8" s="1">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I8" s="1">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1085,34 +1049,34 @@
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="G9" s="1">
-        <v>220</v>
+        <v>483</v>
       </c>
       <c r="H9" s="1">
         <v>90</v>
       </c>
       <c r="I9" s="1">
-        <v>2500</v>
+        <v>25000</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1120,19 +1084,19 @@
         <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G10" s="1">
         <v>350</v>
@@ -1144,10 +1108,10 @@
         <v>10000</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1155,34 +1119,34 @@
         <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="1">
+        <v>423</v>
+      </c>
+      <c r="H11" s="1">
+        <v>88</v>
+      </c>
+      <c r="I11" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" s="1">
-        <v>282</v>
-      </c>
-      <c r="H11" s="1">
-        <v>66</v>
-      </c>
-      <c r="I11" s="1">
-        <v>2500</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="K11" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1190,34 +1154,34 @@
         <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1">
-        <v>181</v>
+        <v>282</v>
       </c>
       <c r="H12" s="1">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I12" s="1">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1225,34 +1189,34 @@
         <v>21</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="1">
+        <v>181</v>
+      </c>
+      <c r="H13" s="1">
+        <v>89</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="1">
-        <v>67</v>
-      </c>
-      <c r="H13" s="1">
-        <v>95</v>
-      </c>
-      <c r="I13" s="1">
-        <v>250000</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="K13" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1260,19 +1224,19 @@
         <v>22</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G14" s="1">
         <v>217</v>
@@ -1284,10 +1248,10 @@
         <v>2500</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1295,34 +1259,34 @@
         <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="1">
+        <v>388</v>
+      </c>
+      <c r="H15" s="1">
         <v>71</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G15" s="1">
-        <v>253</v>
-      </c>
-      <c r="H15" s="1">
-        <v>79</v>
-      </c>
       <c r="I15" s="1">
-        <v>250000</v>
+        <v>10000</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1330,34 +1294,34 @@
         <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="G16" s="1">
-        <v>388</v>
+        <v>53</v>
       </c>
       <c r="H16" s="1">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="I16" s="1">
-        <v>10000</v>
+        <v>250</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1365,69 +1329,34 @@
         <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G17" s="1">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="H17" s="1">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I17" s="1">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="1">
-        <v>95</v>
-      </c>
-      <c r="H18" s="1">
-        <v>64</v>
-      </c>
-      <c r="I18" s="1">
-        <v>500</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1441,65 +1370,60 @@
     <hyperlink ref="F3" r:id="rId7"/>
     <hyperlink ref="K3" r:id="rId8"/>
     <hyperlink ref="A4" r:id="rId9"/>
-    <hyperlink ref="B4" r:id="rId10"/>
-    <hyperlink ref="F4" r:id="rId11"/>
-    <hyperlink ref="K4" r:id="rId12"/>
-    <hyperlink ref="A5" r:id="rId13"/>
-    <hyperlink ref="B5" r:id="rId14"/>
-    <hyperlink ref="F5" r:id="rId15"/>
-    <hyperlink ref="K5" r:id="rId16"/>
-    <hyperlink ref="A6" r:id="rId17"/>
-    <hyperlink ref="B6" r:id="rId18"/>
-    <hyperlink ref="F6" r:id="rId19"/>
-    <hyperlink ref="K6" r:id="rId20"/>
-    <hyperlink ref="A7" r:id="rId21"/>
-    <hyperlink ref="B7" r:id="rId22"/>
-    <hyperlink ref="F7" r:id="rId23"/>
-    <hyperlink ref="K7" r:id="rId24"/>
-    <hyperlink ref="A8" r:id="rId25"/>
-    <hyperlink ref="B8" r:id="rId26"/>
-    <hyperlink ref="F8" r:id="rId27"/>
-    <hyperlink ref="K8" r:id="rId28"/>
-    <hyperlink ref="A9" r:id="rId29"/>
-    <hyperlink ref="B9" r:id="rId30"/>
-    <hyperlink ref="F9" r:id="rId31"/>
-    <hyperlink ref="K9" r:id="rId32"/>
-    <hyperlink ref="A10" r:id="rId33"/>
-    <hyperlink ref="B10" r:id="rId34"/>
-    <hyperlink ref="F10" r:id="rId35"/>
-    <hyperlink ref="K10" r:id="rId36"/>
-    <hyperlink ref="A11" r:id="rId37"/>
-    <hyperlink ref="B11" r:id="rId38"/>
-    <hyperlink ref="F11" r:id="rId39"/>
-    <hyperlink ref="K11" r:id="rId40"/>
-    <hyperlink ref="A12" r:id="rId41"/>
-    <hyperlink ref="B12" r:id="rId42"/>
-    <hyperlink ref="F12" r:id="rId43"/>
-    <hyperlink ref="K12" r:id="rId44"/>
-    <hyperlink ref="A13" r:id="rId45"/>
-    <hyperlink ref="B13" r:id="rId46"/>
-    <hyperlink ref="F13" r:id="rId47"/>
-    <hyperlink ref="K13" r:id="rId48"/>
-    <hyperlink ref="A14" r:id="rId49"/>
-    <hyperlink ref="B14" r:id="rId50"/>
-    <hyperlink ref="F14" r:id="rId51"/>
-    <hyperlink ref="K14" r:id="rId52"/>
-    <hyperlink ref="A15" r:id="rId53"/>
-    <hyperlink ref="B15" r:id="rId54"/>
-    <hyperlink ref="F15" r:id="rId55"/>
-    <hyperlink ref="K15" r:id="rId56"/>
-    <hyperlink ref="A16" r:id="rId57"/>
-    <hyperlink ref="B16" r:id="rId58"/>
-    <hyperlink ref="F16" r:id="rId59"/>
-    <hyperlink ref="K16" r:id="rId60"/>
-    <hyperlink ref="A17" r:id="rId61"/>
-    <hyperlink ref="B17" r:id="rId62"/>
-    <hyperlink ref="F17" r:id="rId63"/>
-    <hyperlink ref="K17" r:id="rId64"/>
-    <hyperlink ref="A18" r:id="rId65"/>
-    <hyperlink ref="B18" r:id="rId66"/>
-    <hyperlink ref="F18" r:id="rId67"/>
-    <hyperlink ref="K18" r:id="rId68"/>
+    <hyperlink ref="F4" r:id="rId10"/>
+    <hyperlink ref="K4" r:id="rId11" location="tab=summary"/>
+    <hyperlink ref="A5" r:id="rId12"/>
+    <hyperlink ref="B5" r:id="rId13"/>
+    <hyperlink ref="F5" r:id="rId14"/>
+    <hyperlink ref="K5" r:id="rId15"/>
+    <hyperlink ref="A6" r:id="rId16"/>
+    <hyperlink ref="B6" r:id="rId17"/>
+    <hyperlink ref="F6" r:id="rId18"/>
+    <hyperlink ref="K6" r:id="rId19"/>
+    <hyperlink ref="A7" r:id="rId20"/>
+    <hyperlink ref="B7" r:id="rId21"/>
+    <hyperlink ref="F7" r:id="rId22"/>
+    <hyperlink ref="K7" r:id="rId23"/>
+    <hyperlink ref="A8" r:id="rId24"/>
+    <hyperlink ref="B8" r:id="rId25"/>
+    <hyperlink ref="F8" r:id="rId26"/>
+    <hyperlink ref="K8" r:id="rId27"/>
+    <hyperlink ref="A9" r:id="rId28"/>
+    <hyperlink ref="B9" r:id="rId29"/>
+    <hyperlink ref="F9" r:id="rId30"/>
+    <hyperlink ref="K9" r:id="rId31"/>
+    <hyperlink ref="A10" r:id="rId32"/>
+    <hyperlink ref="B10" r:id="rId33"/>
+    <hyperlink ref="F10" r:id="rId34"/>
+    <hyperlink ref="K10" r:id="rId35"/>
+    <hyperlink ref="A11" r:id="rId36"/>
+    <hyperlink ref="B11" r:id="rId37"/>
+    <hyperlink ref="F11" r:id="rId38"/>
+    <hyperlink ref="K11" r:id="rId39"/>
+    <hyperlink ref="A12" r:id="rId40"/>
+    <hyperlink ref="B12" r:id="rId41"/>
+    <hyperlink ref="F12" r:id="rId42"/>
+    <hyperlink ref="K12" r:id="rId43"/>
+    <hyperlink ref="A13" r:id="rId44"/>
+    <hyperlink ref="B13" r:id="rId45"/>
+    <hyperlink ref="F13" r:id="rId46"/>
+    <hyperlink ref="K13" r:id="rId47"/>
+    <hyperlink ref="A14" r:id="rId48"/>
+    <hyperlink ref="B14" r:id="rId49"/>
+    <hyperlink ref="F14" r:id="rId50"/>
+    <hyperlink ref="K14" r:id="rId51"/>
+    <hyperlink ref="A15" r:id="rId52"/>
+    <hyperlink ref="B15" r:id="rId53"/>
+    <hyperlink ref="F15" r:id="rId54"/>
+    <hyperlink ref="K15" r:id="rId55"/>
+    <hyperlink ref="A16" r:id="rId56"/>
+    <hyperlink ref="B16" r:id="rId57"/>
+    <hyperlink ref="F16" r:id="rId58"/>
+    <hyperlink ref="K16" r:id="rId59"/>
+    <hyperlink ref="A17" r:id="rId60"/>
+    <hyperlink ref="B17" r:id="rId61"/>
+    <hyperlink ref="F17" r:id="rId62"/>
+    <hyperlink ref="K17" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
